--- a/model_info/gpt_pet.xlsx
+++ b/model_info/gpt_pet.xlsx
@@ -344,7 +344,7 @@
     <col width="4.4" min="12" max="12" bestFit="1" customWidth="1"/>
     <col width="7.700000000000001" min="13" max="13" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -393,7 +393,7 @@
         <v>0.06464154043889171</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.07936507936507937</v>
+        <v>0.4615575396825397</v>
       </c>
     </row>
     <row r="2">
@@ -442,7 +442,7 @@
         <v>0.3975939569912922</v>
       </c>
       <c r="O2" s="0" t="n">
-        <v>0.14242424242424245</v>
+        <v>0.5071095571095572</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         <v>0.22776870869288296</v>
       </c>
       <c r="O3" s="0" t="n">
-        <v>0.06666666666666665</v>
+        <v>0.5333333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -540,7 +540,7 @@
         <v>0.12013023348079402</v>
       </c>
       <c r="O4" s="0" t="n">
-        <v>0.09090909090909088</v>
+        <v>0.516042780748663</v>
       </c>
     </row>
     <row r="5">
@@ -589,7 +589,7 @@
         <v>0.6680082317942931</v>
       </c>
       <c r="O5" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="6">
@@ -638,7 +638,7 @@
         <v>0.7327542951207594</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.9116161616161615</v>
       </c>
     </row>
     <row r="7">
@@ -687,7 +687,7 @@
         <v>0.0</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>0.0</v>
+        <v>0.467741935483871</v>
       </c>
     </row>
     <row r="8">
@@ -736,7 +736,7 @@
         <v>0.7733570130087944</v>
       </c>
       <c r="O8" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="9">
@@ -785,7 +785,7 @@
         <v>0.15771305210596048</v>
       </c>
       <c r="O9" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10">
@@ -834,7 +834,7 @@
         <v>0.0</v>
       </c>
       <c r="O10" s="0" t="n">
-        <v>0.03333333333333334</v>
+        <v>0.35000000000000003</v>
       </c>
     </row>
     <row r="11">
@@ -883,7 +883,7 @@
         <v>0.5198452137313996</v>
       </c>
       <c r="O11" s="0" t="n">
-        <v>0.13952020202020202</v>
+        <v>0.509760101010101</v>
       </c>
     </row>
     <row r="12">
@@ -932,7 +932,7 @@
         <v>0.3313196276671509</v>
       </c>
       <c r="O12" s="0" t="n">
-        <v>0.3568181818181818</v>
+        <v>0.6575757575757576</v>
       </c>
     </row>
     <row r="13">
@@ -981,7 +981,7 @@
         <v>0.369382115699648</v>
       </c>
       <c r="O13" s="0" t="n">
-        <v>0.09722222222222222</v>
+        <v>0.4880050505050505</v>
       </c>
     </row>
     <row r="14">
@@ -1030,7 +1030,7 @@
         <v>0.6226121871688631</v>
       </c>
       <c r="O14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6833333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -1079,7 +1079,7 @@
         <v>0.3731602740671912</v>
       </c>
       <c r="O15" s="0" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="16">
@@ -1128,7 +1128,7 @@
         <v>0.2959247023626196</v>
       </c>
       <c r="O16" s="0" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="17">
@@ -1177,7 +1177,7 @@
         <v>0.38706940315909666</v>
       </c>
       <c r="O17" s="0" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="18">
@@ -1275,7 +1275,7 @@
         <v>0.37283664601365796</v>
       </c>
       <c r="O19" s="0" t="n">
-        <v>0.2824254223251969</v>
+        <v>0.6364508064006937</v>
       </c>
     </row>
     <row r="20">
@@ -1324,7 +1324,7 @@
         <v>0.169041681584197</v>
       </c>
       <c r="O20" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="21">
@@ -1373,7 +1373,7 @@
         <v>0.10653098097165183</v>
       </c>
       <c r="O21" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="22">
@@ -1422,7 +1422,7 @@
         <v>0.7482695165801455</v>
       </c>
       <c r="O22" s="0" t="n">
-        <v>0.6398809523809523</v>
+        <v>0.8199404761904762</v>
       </c>
     </row>
     <row r="23">
@@ -1471,7 +1471,7 @@
         <v>0.12390739552493286</v>
       </c>
       <c r="O23" s="0" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="24">
@@ -1520,7 +1520,7 @@
         <v>0.5637113501615687</v>
       </c>
       <c r="O24" s="0" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.8506944444444444</v>
       </c>
     </row>
     <row r="25">
@@ -1569,7 +1569,7 @@
         <v>0.22241680801619074</v>
       </c>
       <c r="O25" s="0" t="n">
-        <v>0.16103051629787066</v>
+        <v>0.5577879854216626</v>
       </c>
     </row>
     <row r="26">
@@ -1618,7 +1618,7 @@
         <v>0.394182612530914</v>
       </c>
       <c r="O26" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7916666666666667</v>
       </c>
     </row>
     <row r="27">
@@ -1667,7 +1667,7 @@
         <v>0.37293135466510197</v>
       </c>
       <c r="O27" s="0" t="n">
-        <v>0.55</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="28">
@@ -1716,7 +1716,7 @@
         <v>0.06471645749022141</v>
       </c>
       <c r="O28" s="0" t="n">
-        <v>0.014906043389015525</v>
+        <v>0.2574530216945078</v>
       </c>
     </row>
     <row r="29">
@@ -1765,7 +1765,7 @@
         <v>0.1129192205075518</v>
       </c>
       <c r="O29" s="0" t="n">
-        <v>0.1490251897860594</v>
+        <v>0.4600547635677285</v>
       </c>
     </row>
     <row r="30">
@@ -1814,7 +1814,7 @@
         <v>0.5500949776949183</v>
       </c>
       <c r="O30" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="31">
@@ -1863,7 +1863,7 @@
         <v>0.5127400440851051</v>
       </c>
       <c r="O31" s="0" t="n">
-        <v>0.5777777777777777</v>
+        <v>0.7888888888888889</v>
       </c>
     </row>
     <row r="32">
@@ -1912,7 +1912,7 @@
         <v>0.27664055714952307</v>
       </c>
       <c r="O32" s="0" t="n">
-        <v>0.13168724279835395</v>
+        <v>0.465843621399177</v>
       </c>
     </row>
     <row r="33">
@@ -1961,7 +1961,7 @@
         <v>0.22530022811809994</v>
       </c>
       <c r="O33" s="0" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6428571428571428</v>
       </c>
     </row>
     <row r="34">
@@ -2010,7 +2010,7 @@
         <v>0.1915609682512433</v>
       </c>
       <c r="O34" s="0" t="n">
-        <v>0.0625</v>
+        <v>0.40625</v>
       </c>
     </row>
     <row r="35">
@@ -2059,7 +2059,7 @@
         <v>0.8030320640514111</v>
       </c>
       <c r="O35" s="0" t="n">
-        <v>0.5902856691919189</v>
+        <v>0.7747346713306533</v>
       </c>
     </row>
     <row r="36">
@@ -2108,7 +2108,7 @@
         <v>0.4741700875342542</v>
       </c>
       <c r="O36" s="0" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.7324929971988796</v>
       </c>
     </row>
     <row r="37">
@@ -2157,7 +2157,7 @@
         <v>0.58291281191333</v>
       </c>
       <c r="O37" s="0" t="n">
-        <v>0.14814814814814814</v>
+        <v>0.4740740740740741</v>
       </c>
     </row>
     <row r="38">
@@ -2206,7 +2206,7 @@
         <v>0.7026559828077152</v>
       </c>
       <c r="O38" s="0" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
   </sheetData>

--- a/model_info/gpt_pet.xlsx
+++ b/model_info/gpt_pet.xlsx
@@ -344,7 +344,7 @@
     <col width="4.4" min="12" max="12" bestFit="1" customWidth="1"/>
     <col width="7.700000000000001" min="13" max="13" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="15" max="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -393,7 +393,7 @@
         <v>0.06464154043889171</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.4615575396825397</v>
+        <v>0.06696428571428573</v>
       </c>
     </row>
     <row r="2">
@@ -442,7 +442,7 @@
         <v>0.3975939569912922</v>
       </c>
       <c r="O2" s="0" t="n">
-        <v>0.5071095571095572</v>
+        <v>0.1241647241647242</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +491,7 @@
         <v>0.22776870869288296</v>
       </c>
       <c r="O3" s="0" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.06666666666666665</v>
       </c>
     </row>
     <row r="4">
@@ -540,7 +540,7 @@
         <v>0.12013023348079402</v>
       </c>
       <c r="O4" s="0" t="n">
-        <v>0.516042780748663</v>
+        <v>0.08556149732620319</v>
       </c>
     </row>
     <row r="5">
@@ -589,7 +589,7 @@
         <v>0.6680082317942931</v>
       </c>
       <c r="O5" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6">
@@ -638,7 +638,7 @@
         <v>0.7327542951207594</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>0.9116161616161615</v>
+        <v>0.8299663299663299</v>
       </c>
     </row>
     <row r="7">
@@ -687,7 +687,7 @@
         <v>0.0</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>0.467741935483871</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -736,7 +736,7 @@
         <v>0.7733570130087944</v>
       </c>
       <c r="O8" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="9">
@@ -785,7 +785,7 @@
         <v>0.15771305210596048</v>
       </c>
       <c r="O9" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
     </row>
     <row r="10">
@@ -834,7 +834,7 @@
         <v>0.0</v>
       </c>
       <c r="O10" s="0" t="n">
-        <v>0.35000000000000003</v>
+        <v>0.02222222222222223</v>
       </c>
     </row>
     <row r="11">
@@ -883,7 +883,7 @@
         <v>0.5198452137313996</v>
       </c>
       <c r="O11" s="0" t="n">
-        <v>0.509760101010101</v>
+        <v>0.12277777777777778</v>
       </c>
     </row>
     <row r="12">
@@ -932,7 +932,7 @@
         <v>0.3313196276671509</v>
       </c>
       <c r="O12" s="0" t="n">
-        <v>0.6575757575757576</v>
+        <v>0.3419507575757576</v>
       </c>
     </row>
     <row r="13">
@@ -981,7 +981,7 @@
         <v>0.369382115699648</v>
       </c>
       <c r="O13" s="0" t="n">
-        <v>0.4880050505050505</v>
+        <v>0.08543771043771044</v>
       </c>
     </row>
     <row r="14">
@@ -1030,7 +1030,7 @@
         <v>0.6226121871688631</v>
       </c>
       <c r="O14" s="0" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.43333333333333335</v>
       </c>
     </row>
     <row r="15">
@@ -1079,7 +1079,7 @@
         <v>0.3731602740671912</v>
       </c>
       <c r="O15" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16">
@@ -1128,7 +1128,7 @@
         <v>0.2959247023626196</v>
       </c>
       <c r="O16" s="0" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.4285714285714286</v>
       </c>
     </row>
     <row r="17">
@@ -1177,7 +1177,7 @@
         <v>0.38706940315909666</v>
       </c>
       <c r="O17" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
@@ -1275,7 +1275,7 @@
         <v>0.37283664601365796</v>
       </c>
       <c r="O19" s="0" t="n">
-        <v>0.6364508064006937</v>
+        <v>0.2797356563982903</v>
       </c>
     </row>
     <row r="20">
@@ -1324,7 +1324,7 @@
         <v>0.169041681584197</v>
       </c>
       <c r="O20" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
     </row>
     <row r="21">
@@ -1373,7 +1373,7 @@
         <v>0.10653098097165183</v>
       </c>
       <c r="O21" s="0" t="n">
-        <v>0.55</v>
+        <v>0.09999999999999998</v>
       </c>
     </row>
     <row r="22">
@@ -1422,7 +1422,7 @@
         <v>0.7482695165801455</v>
       </c>
       <c r="O22" s="0" t="n">
-        <v>0.8199404761904762</v>
+        <v>0.6398809523809523</v>
       </c>
     </row>
     <row r="23">
@@ -1471,7 +1471,7 @@
         <v>0.12390739552493286</v>
       </c>
       <c r="O23" s="0" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571429</v>
       </c>
     </row>
     <row r="24">
@@ -1520,7 +1520,7 @@
         <v>0.5637113501615687</v>
       </c>
       <c r="O24" s="0" t="n">
-        <v>0.8506944444444444</v>
+        <v>0.7013888888888888</v>
       </c>
     </row>
     <row r="25">
@@ -1569,7 +1569,7 @@
         <v>0.22241680801619074</v>
       </c>
       <c r="O25" s="0" t="n">
-        <v>0.5577879854216626</v>
+        <v>0.1537109473752402</v>
       </c>
     </row>
     <row r="26">
@@ -1618,7 +1618,7 @@
         <v>0.394182612530914</v>
       </c>
       <c r="O26" s="0" t="n">
-        <v>0.7916666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="27">
@@ -1667,7 +1667,7 @@
         <v>0.37293135466510197</v>
       </c>
       <c r="O27" s="0" t="n">
-        <v>0.775</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="28">
@@ -1716,7 +1716,7 @@
         <v>0.06471645749022141</v>
       </c>
       <c r="O28" s="0" t="n">
-        <v>0.2574530216945078</v>
+        <v>0.007453021694507763</v>
       </c>
     </row>
     <row r="29">
@@ -1765,7 +1765,7 @@
         <v>0.1129192205075518</v>
       </c>
       <c r="O29" s="0" t="n">
-        <v>0.4600547635677285</v>
+        <v>0.11491098971455183</v>
       </c>
     </row>
     <row r="30">
@@ -1814,7 +1814,7 @@
         <v>0.5500949776949183</v>
       </c>
       <c r="O30" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
     </row>
     <row r="31">
@@ -1863,7 +1863,7 @@
         <v>0.5127400440851051</v>
       </c>
       <c r="O31" s="0" t="n">
-        <v>0.7888888888888889</v>
+        <v>0.5777777777777777</v>
       </c>
     </row>
     <row r="32">
@@ -1912,7 +1912,7 @@
         <v>0.27664055714952307</v>
       </c>
       <c r="O32" s="0" t="n">
-        <v>0.465843621399177</v>
+        <v>0.10534979423868317</v>
       </c>
     </row>
     <row r="33">
@@ -1961,7 +1961,7 @@
         <v>0.22530022811809994</v>
       </c>
       <c r="O33" s="0" t="n">
-        <v>0.6428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="34">
@@ -2010,7 +2010,7 @@
         <v>0.1915609682512433</v>
       </c>
       <c r="O34" s="0" t="n">
-        <v>0.40625</v>
+        <v>0.046875</v>
       </c>
     </row>
     <row r="35">
@@ -2059,7 +2059,7 @@
         <v>0.8030320640514111</v>
       </c>
       <c r="O35" s="0" t="n">
-        <v>0.7747346713306533</v>
+        <v>0.5661923765718406</v>
       </c>
     </row>
     <row r="36">
@@ -2108,7 +2108,7 @@
         <v>0.4741700875342542</v>
       </c>
       <c r="O36" s="0" t="n">
-        <v>0.7324929971988796</v>
+        <v>0.49299719887955185</v>
       </c>
     </row>
     <row r="37">
@@ -2157,7 +2157,7 @@
         <v>0.58291281191333</v>
       </c>
       <c r="O37" s="0" t="n">
-        <v>0.4740740740740741</v>
+        <v>0.11851851851851852</v>
       </c>
     </row>
     <row r="38">
@@ -2206,7 +2206,7 @@
         <v>0.7026559828077152</v>
       </c>
       <c r="O38" s="0" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
